--- a/assessment_forms/006_relationship_self_assessment_questionnaire--assessment_forms.xlsx
+++ b/assessment_forms/006_relationship_self_assessment_questionnaire--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -963,7 +963,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Relationship Expectations</t>
+          <t>Relationship Expectations Health</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -986,7 +986,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Partner Employment Status</t>
+          <t>Partner Employment Status Health</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Partner Employment Education</t>
+          <t>Partner Employment Education Health</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>partner_employment_education_health</t>
+          <t>partner_employment_education_health_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Partner Employment Education</t>
+          <t>Partner Employment Education Health 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Conflict Frequency</t>
+          <t>Conflict Frequency Health</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Conflict Resolution</t>
+          <t>Conflict Resolution Health</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>relationship_expectations_health</t>
+          <t>relationship_expectations_health_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Relationship Expectations</t>
+          <t>Relationship Expectations Health 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
   <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
@@ -2323,7 +2323,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>partner_employment_education_health_choices</t>
+          <t>partner_employment_education_health_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2340,7 +2340,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>partner_employment_education_health_choices</t>
+          <t>partner_employment_education_health_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>partner_employment_education_health_choices</t>
+          <t>partner_employment_education_health_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>partner_employment_education_health_choices</t>
+          <t>partner_employment_education_health_2_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>partner_employment_education_health_choices</t>
+          <t>partner_employment_education_health_2_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>partner_employment_education_health_choices</t>
+          <t>partner_employment_education_health_2_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>partner_employment_education_health_choices</t>
+          <t>partner_employment_education_health_2_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>relationship_expectations_health_choices</t>
+          <t>relationship_expectations_health_2_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>relationship_expectations_health_choices</t>
+          <t>relationship_expectations_health_2_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2612,7 +2612,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>relationship_expectations_health_choices</t>
+          <t>relationship_expectations_health_2_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
